--- a/internship_artifacts/Unit_Test_Plan_v0.1.xlsx
+++ b/internship_artifacts/Unit_Test_Plan_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infosystechnologies-my.sharepoint.com/personal/kamaljeet_kaur01_ad_infosys_com1/Documents/Infosys/CC/Events/Oct 2021 - Mar 2022/CC2.0/Internship/Jan-Apr 2022/Artifacts/internship/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38a153e61142a931/Desktop/AI_SMART_BUG_ANALYZER_FIX_ADVISOR/internship_artifacts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5C97600-B903-4DC3-995C-1AC2F6826551}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="UT" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>Actual Result</t>
   </si>
@@ -52,6 +52,105 @@
   </si>
   <si>
     <t>Sl: No:</t>
+  </si>
+  <si>
+    <t>Upload Valid Bug Report</t>
+  </si>
+  <si>
+    <t>Upload Invalid File</t>
+  </si>
+  <si>
+    <t>Empty File Upload</t>
+  </si>
+  <si>
+    <t>Generate Embeddings</t>
+  </si>
+  <si>
+    <t>Retrieve Similar Bugs</t>
+  </si>
+  <si>
+    <t>Execute Triage Agent</t>
+  </si>
+  <si>
+    <t>Execute Log Analysis Agent</t>
+  </si>
+  <si>
+    <t>Generate Fix Recommendation</t>
+  </si>
+  <si>
+    <t>Upload a valid TXT file</t>
+  </si>
+  <si>
+    <t>Upload PDF/EXE</t>
+  </si>
+  <si>
+    <t>Upload empty TXT</t>
+  </si>
+  <si>
+    <t>Run embedding model</t>
+  </si>
+  <si>
+    <t>Search using a  bug report</t>
+  </si>
+  <si>
+    <t>Submit bug</t>
+  </si>
+  <si>
+    <t>Upload stack trace</t>
+  </si>
+  <si>
+    <t>Run analysis</t>
+  </si>
+  <si>
+    <t>Root cause available</t>
+  </si>
+  <si>
+    <t>Valid log</t>
+  </si>
+  <si>
+    <t>Valid bug report</t>
+  </si>
+  <si>
+    <t>Existing bugs in dataset</t>
+  </si>
+  <si>
+    <t>Valid bug text</t>
+  </si>
+  <si>
+    <t>Empty file</t>
+  </si>
+  <si>
+    <t>Invalid format</t>
+  </si>
+  <si>
+    <t>Valid TXT file</t>
+  </si>
+  <si>
+    <t>Bug uploaded successfully</t>
+  </si>
+  <si>
+    <t>Error message displayed</t>
+  </si>
+  <si>
+    <t>Validation message shown</t>
+  </si>
+  <si>
+    <t>Embeddings generated</t>
+  </si>
+  <si>
+    <t>Similar bugs displayed</t>
+  </si>
+  <si>
+    <t>Severity predicted</t>
+  </si>
+  <si>
+    <t>Exception identified</t>
+  </si>
+  <si>
+    <t>Fix recommendation generated</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
@@ -94,7 +193,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -117,16 +216,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -147,9 +260,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +300,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -293,7 +406,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,7 +548,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -443,17 +556,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="4" max="5" width="16.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -473,45 +586,165 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+    <row r="2" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="46.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="46.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="46.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
